--- a/Templates~/Config/Excels/L10n/__tables__.xlsx
+++ b/Templates~/Config/Excels/L10n/__tables__.xlsx
@@ -1,37 +1,186 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Workspace\Unity\Game Dev Tools\Config\Excels\L10n\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B8F0FBD-C761-459C-9C88-A7AD460FF395}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="5325" yWindow="5325" windowWidth="28815" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="40">
+  <si>
+    <t>##var</t>
+  </si>
+  <si>
+    <t>full_name</t>
+  </si>
+  <si>
+    <t>value_type</t>
+  </si>
+  <si>
+    <t>read_schema_from_file</t>
+  </si>
+  <si>
+    <t>input</t>
+  </si>
+  <si>
+    <t>index</t>
+  </si>
+  <si>
+    <t>mode</t>
+  </si>
+  <si>
+    <t>group</t>
+  </si>
+  <si>
+    <t>comment</t>
+  </si>
+  <si>
+    <t>tags</t>
+  </si>
+  <si>
+    <t>output</t>
+  </si>
+  <si>
+    <t>##</t>
+  </si>
+  <si>
+    <t>全名(包含模块和名字)</t>
+  </si>
+  <si>
+    <t>记录类名</t>
+  </si>
+  <si>
+    <t>从excel读取定义</t>
+  </si>
+  <si>
+    <t>文件列表</t>
+  </si>
+  <si>
+    <t>表id字段</t>
+  </si>
+  <si>
+    <t>模式</t>
+  </si>
+  <si>
+    <t>分组</t>
+  </si>
+  <si>
+    <t>注释</t>
+  </si>
+  <si>
+    <t>输出文件名</t>
+  </si>
+  <si>
+    <t>false时取已有定义，true为从excel标题头和属性栏读取定义</t>
+  </si>
+  <si>
+    <t>可以多个，以逗号','分隔</t>
+  </si>
+  <si>
+    <t>为空的话自动取value_type中第一个字段,多主键联合索引为key1+key2,多主键独立索引为"key1,key2"</t>
+  </si>
+  <si>
+    <t>取值one|map|list，为空自动为map</t>
+  </si>
+  <si>
+    <t>取值c|s|e，可以有多个，以逗号','分隔。空则表示属于所有分组</t>
+  </si>
+  <si>
+    <t>默认为 &lt;module&gt;_&lt;name&gt;.&lt;suffix&gt;</t>
+  </si>
+  <si>
+    <t>L10n.TbLocalizedStrings</t>
+  </si>
+  <si>
+    <t>LocalizedStringsConfig</t>
+  </si>
+  <si>
+    <t>L10n/LocalizedStrings.xlsx</t>
+  </si>
+  <si>
+    <t>c</t>
+  </si>
+  <si>
+    <t>多语言词条配置</t>
+  </si>
+  <si>
+    <t>L10n.TbLocalizedAudio</t>
+  </si>
+  <si>
+    <t>LocalizedAudioConfig</t>
+  </si>
+  <si>
+    <t>L10n/LocalizedAudio.xlsx</t>
+  </si>
+  <si>
+    <t>多语言音频配置</t>
+  </si>
+  <si>
+    <t>L10n.TbLocalizedImages</t>
+  </si>
+  <si>
+    <t>LocalizedImagesConfig</t>
+  </si>
+  <si>
+    <t>L10n/LocalizedImages.xlsx</t>
+  </si>
+  <si>
+    <t>多语言图片配置</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
-      <name val="Calibri"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
       <family val="2"/>
-      <color theme="1"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -43,84 +192,30 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyAlignment="1"/>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+  <cellStyles count="2">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="好" xfId="1" builtinId="26"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -408,251 +503,175 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <cols>
+    <col min="1" max="1" width="6.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="25" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="24.25" customWidth="1"/>
+    <col min="5" max="5" width="29.375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.375" customWidth="1"/>
+    <col min="7" max="7" width="19.25" customWidth="1"/>
+    <col min="8" max="8" width="10.875" customWidth="1"/>
+    <col min="9" max="9" width="15.125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="5.5" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="34.5" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>##var</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>full_name</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>value_type</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>read_schema_from_file</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>input</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>index</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>mode</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>group</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>comment</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>tags</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>output</t>
-        </is>
+    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>##</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>全名(包含模块和名字)</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>记录类名</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>从excel读取定义</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>文件列表</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>表id字段</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>模式</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>分组</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>注释</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>输出文件名</t>
-        </is>
+    <row r="2" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>20</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>##</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>false时取已有定义，true为从excel标题头和属性栏读取定义</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>可以多个，以逗号','分隔</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>为空的话自动取value_type中第一个字段,多主键联合索引为key1+key2,多主键独立索引为"key1,key2"</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>取值one|map|list，为空自动为map</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>取值c|s|e，可以有多个，以逗号','分隔。空则表示属于所有分组</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>默认为 &lt;module&gt;_&lt;name&gt;.&lt;suffix&gt;</t>
-        </is>
+    <row r="3" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>26</v>
       </c>
     </row>
-    <row r="4">
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>L10n.TbLocalizedStrings</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>LocalizedStringsConfig</t>
-        </is>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="B4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" t="s">
+        <v>28</v>
       </c>
       <c r="D4" t="b">
         <v>1</v>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>L10n/LocalizedStrings.xlsx</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>多语言词条配置</t>
-        </is>
+      <c r="E4" t="s">
+        <v>29</v>
+      </c>
+      <c r="H4" t="s">
+        <v>30</v>
+      </c>
+      <c r="I4" t="s">
+        <v>31</v>
       </c>
     </row>
-    <row r="5">
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>L10n.TbLocalizedAudio</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>LocalizedAudioConfig</t>
-        </is>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="B5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C5" t="s">
+        <v>33</v>
       </c>
       <c r="D5" t="b">
         <v>1</v>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>L10n/LocalizedAudio.xlsx</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>多语言音频配置</t>
-        </is>
+      <c r="E5" t="s">
+        <v>34</v>
+      </c>
+      <c r="H5" t="s">
+        <v>30</v>
+      </c>
+      <c r="I5" t="s">
+        <v>35</v>
       </c>
     </row>
-    <row r="6">
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>L10n.TbLocalizedImages</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>LocalizedImagesConfig</t>
-        </is>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="B6" t="s">
+        <v>36</v>
+      </c>
+      <c r="C6" t="s">
+        <v>37</v>
       </c>
       <c r="D6" t="b">
         <v>1</v>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>L10n/LocalizedImages.xlsx</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>多语言图片配置</t>
-        </is>
+      <c r="E6" t="s">
+        <v>38</v>
+      </c>
+      <c r="H6" t="s">
+        <v>30</v>
+      </c>
+      <c r="I6" t="s">
+        <v>39</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>